--- a/engine_package/Res/MuDataEditor/天使之战_v1.0.0.0/In/cfg_global.xlsx
+++ b/engine_package/Res/MuDataEditor/天使之战_v1.0.0.0/In/cfg_global.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255"/>
+    <workbookView windowWidth="28800" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="cfg_global" sheetId="1" r:id="rId1"/>
@@ -1038,7 +1038,7 @@
     <t>角色等级每升1级给的通用天赋点数</t>
   </si>
   <si>
-    <t>350#400</t>
+    <t>750#800</t>
   </si>
   <si>
     <t>获得通用天赋点的开始结束等级（格式：开始等级#结束等级）</t>
@@ -1506,7 +1506,7 @@
     <t>商城右下角显示</t>
   </si>
   <si>
-    <t>金币#10010001#10010002|积分#10240001</t>
+    <t>金币#10010001#10010002|积分#10240001|瑞币#10040001</t>
   </si>
   <si>
     <t>名称#道具id#道具id（显示所有配置道具id数量之和）</t>
@@ -1518,7 +1518,7 @@
     <t>交易行右下角显示</t>
   </si>
   <si>
-    <t>10010001|10240001</t>
+    <t>10010001|10040001</t>
   </si>
   <si>
     <t>道具id|道具id</t>
@@ -5351,7 +5351,7 @@
         <v>66</v>
       </c>
       <c r="C104" s="13">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D104" s="13" t="s">
         <v>203</v>
@@ -6160,7 +6160,7 @@
         <v>291</v>
       </c>
       <c r="C162" s="13">
-        <v>300</v>
+        <v>700</v>
       </c>
       <c r="D162" s="13" t="s">
         <v>312</v>
@@ -7548,9 +7548,7 @@
       <c r="B262" s="1" t="s">
         <v>527</v>
       </c>
-      <c r="C262" s="1">
-        <v>15</v>
-      </c>
+      <c r="C262" s="1"/>
       <c r="D262" s="1" t="s">
         <v>524</v>
       </c>
@@ -8654,7 +8652,7 @@
       <c r="B341" s="11" t="s">
         <v>464</v>
       </c>
-      <c r="C341" s="11" t="s">
+      <c r="C341" s="5" t="s">
         <v>465</v>
       </c>
       <c r="D341" s="11" t="s">
@@ -9374,7 +9372,7 @@
         <v>817</v>
       </c>
       <c r="C393" s="10">
-        <v>12</v>
+        <v>40</v>
       </c>
       <c r="D393" s="10" t="s">
         <v>818</v>
@@ -9388,7 +9386,7 @@
         <v>819</v>
       </c>
       <c r="C394" s="10">
-        <v>12</v>
+        <v>40</v>
       </c>
       <c r="D394" s="10" t="s">
         <v>820</v>

--- a/engine_package/Res/MuDataEditor/天使之战_v1.0.0.0/In/cfg_global.xlsx
+++ b/engine_package/Res/MuDataEditor/天使之战_v1.0.0.0/In/cfg_global.xlsx
@@ -3,8 +3,13 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\天使之战\tszz_GMTest\engine_package\Res\MuDataEditor\天使之战_v1.0.0.0\In\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="cfg_global" sheetId="1" r:id="rId1"/>
@@ -1536,7 +1541,7 @@
     <t>总览属性（2套）傲视上面也这么显示</t>
   </si>
   <si>
-    <t>201011#10|201021#6|207011#500</t>
+    <t>200041#50|206011#50|200042#500</t>
   </si>
   <si>
     <t>玩家集齐所有套装后获得的属性（2套）</t>
@@ -1545,7 +1550,7 @@
     <t>总览属性（3套）傲视上面也这么显示</t>
   </si>
   <si>
-    <t>201011#10|201021#6|207011#500|311112#200</t>
+    <t>200041#150|206011#150|200042#800</t>
   </si>
   <si>
     <t>玩家集齐所有套装后获得的属性（3套）</t>
@@ -1554,7 +1559,7 @@
     <t>总览属性（4套）傲视上面也这么显示</t>
   </si>
   <si>
-    <t>201011#10|201021#6|207011#500|311112#200|312112#200</t>
+    <t>200041#350|206011#350|200042#1500</t>
   </si>
   <si>
     <t>玩家集齐所有套装后获得的属性（4套）</t>
@@ -1899,7 +1904,7 @@
     <t>选角界面系统提示</t>
   </si>
   <si>
-    <t>系统提示:版本还原1.03H\n技术支持:雷霆纪元研发团队</t>
+    <t>系统提示:正版游戏，拒绝盗版。严谨使用第三方辅助。一经发现永久封禁。</t>
   </si>
   <si>
     <t>选角界面左上角的系统提示</t>
@@ -3374,7 +3379,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -3431,6 +3436,9 @@
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -6160,7 +6168,7 @@
         <v>291</v>
       </c>
       <c r="C162" s="13">
-        <v>700</v>
+        <v>400</v>
       </c>
       <c r="D162" s="13" t="s">
         <v>312</v>
@@ -7275,14 +7283,14 @@
         <v>473</v>
       </c>
     </row>
-    <row r="243" s="4" customFormat="1" spans="1:4">
+    <row r="243" s="4" customFormat="1" ht="15" spans="1:4">
       <c r="A243" s="4">
         <v>280001</v>
       </c>
       <c r="B243" s="4" t="s">
         <v>474</v>
       </c>
-      <c r="C243" s="4" t="s">
+      <c r="C243" s="20" t="s">
         <v>475</v>
       </c>
       <c r="D243" s="4" t="s">
@@ -7422,7 +7430,7 @@
       <c r="B253" s="4" t="s">
         <v>501</v>
       </c>
-      <c r="C253" s="20" t="s">
+      <c r="C253" s="21" t="s">
         <v>502</v>
       </c>
       <c r="D253" s="4" t="s">
@@ -7436,7 +7444,7 @@
       <c r="B254" s="4" t="s">
         <v>504</v>
       </c>
-      <c r="C254" s="20" t="s">
+      <c r="C254" s="21" t="s">
         <v>505</v>
       </c>
       <c r="D254" s="4" t="s">
@@ -7450,7 +7458,7 @@
       <c r="B255" s="4" t="s">
         <v>507</v>
       </c>
-      <c r="C255" s="20" t="s">
+      <c r="C255" s="21" t="s">
         <v>508</v>
       </c>
       <c r="D255" s="4" t="s">
@@ -7464,7 +7472,7 @@
       <c r="B256" s="4" t="s">
         <v>510</v>
       </c>
-      <c r="C256" s="21" t="s">
+      <c r="C256" s="22" t="s">
         <v>511</v>
       </c>
       <c r="D256" s="4" t="s">
@@ -7478,7 +7486,7 @@
       <c r="B257" s="4" t="s">
         <v>513</v>
       </c>
-      <c r="C257" s="21" t="s">
+      <c r="C257" s="22" t="s">
         <v>514</v>
       </c>
       <c r="D257" s="4" t="s">
@@ -7492,7 +7500,7 @@
       <c r="B258" s="4" t="s">
         <v>516</v>
       </c>
-      <c r="C258" s="20" t="s">
+      <c r="C258" s="21" t="s">
         <v>517</v>
       </c>
       <c r="D258" s="4" t="s">
@@ -7506,7 +7514,7 @@
       <c r="B259" s="4" t="s">
         <v>519</v>
       </c>
-      <c r="C259" s="21" t="s">
+      <c r="C259" s="22" t="s">
         <v>520</v>
       </c>
       <c r="D259" s="4" t="s">
@@ -7812,7 +7820,7 @@
       <c r="B281" s="4" t="s">
         <v>570</v>
       </c>
-      <c r="C281" s="21" t="s">
+      <c r="C281" s="22" t="s">
         <v>571</v>
       </c>
       <c r="D281" s="4" t="s">
@@ -7826,7 +7834,7 @@
       <c r="B282" s="4" t="s">
         <v>572</v>
       </c>
-      <c r="C282" s="20" t="s">
+      <c r="C282" s="21" t="s">
         <v>573</v>
       </c>
       <c r="D282" s="4" t="s">
@@ -7840,7 +7848,7 @@
       <c r="B283" s="4" t="s">
         <v>574</v>
       </c>
-      <c r="C283" s="20" t="s">
+      <c r="C283" s="21" t="s">
         <v>575</v>
       </c>
       <c r="D283" s="4" t="s">
@@ -7854,7 +7862,7 @@
       <c r="B284" s="4" t="s">
         <v>576</v>
       </c>
-      <c r="C284" s="21" t="s">
+      <c r="C284" s="22" t="s">
         <v>577</v>
       </c>
       <c r="D284" s="4" t="s">
@@ -7882,7 +7890,7 @@
       <c r="B286" s="1" t="s">
         <v>581</v>
       </c>
-      <c r="C286" s="28" t="s">
+      <c r="C286" s="29" t="s">
         <v>582</v>
       </c>
       <c r="D286" s="1" t="s">
@@ -7938,7 +7946,7 @@
       <c r="B290" s="1" t="s">
         <v>592</v>
       </c>
-      <c r="C290" s="28" t="s">
+      <c r="C290" s="29" t="s">
         <v>593</v>
       </c>
       <c r="D290" s="1" t="s">
@@ -7966,7 +7974,7 @@
       <c r="B292" s="1" t="s">
         <v>598</v>
       </c>
-      <c r="C292" s="28" t="s">
+      <c r="C292" s="29" t="s">
         <v>599</v>
       </c>
       <c r="D292" s="1" t="s">
@@ -8067,7 +8075,7 @@
       <c r="C299" s="4" t="s">
         <v>616</v>
       </c>
-      <c r="D299" s="22" t="s">
+      <c r="D299" s="23" t="s">
         <v>617</v>
       </c>
     </row>
@@ -8162,7 +8170,7 @@
       <c r="B306" s="4" t="s">
         <v>634</v>
       </c>
-      <c r="C306" s="20" t="s">
+      <c r="C306" s="21" t="s">
         <v>635</v>
       </c>
       <c r="D306" s="4" t="s">
@@ -8176,7 +8184,7 @@
       <c r="B307" s="4" t="s">
         <v>637</v>
       </c>
-      <c r="C307" s="20" t="s">
+      <c r="C307" s="21" t="s">
         <v>635</v>
       </c>
       <c r="D307" s="4" t="s">
@@ -8190,7 +8198,7 @@
       <c r="B308" s="4" t="s">
         <v>639</v>
       </c>
-      <c r="C308" s="20" t="s">
+      <c r="C308" s="21" t="s">
         <v>640</v>
       </c>
       <c r="D308" s="4" t="s">
@@ -8204,7 +8212,7 @@
       <c r="B309" s="4" t="s">
         <v>642</v>
       </c>
-      <c r="C309" s="20" t="s">
+      <c r="C309" s="21" t="s">
         <v>643</v>
       </c>
       <c r="D309" s="4" t="s">
@@ -8218,7 +8226,7 @@
       <c r="B310" s="4" t="s">
         <v>645</v>
       </c>
-      <c r="C310" s="20" t="s">
+      <c r="C310" s="21" t="s">
         <v>646</v>
       </c>
       <c r="D310" s="4" t="s">
@@ -8232,7 +8240,7 @@
       <c r="B311" s="4" t="s">
         <v>648</v>
       </c>
-      <c r="C311" s="20" t="s">
+      <c r="C311" s="21" t="s">
         <v>646</v>
       </c>
       <c r="D311" s="4" t="s">
@@ -8246,7 +8254,7 @@
       <c r="B312" s="4" t="s">
         <v>649</v>
       </c>
-      <c r="C312" s="20" t="s">
+      <c r="C312" s="21" t="s">
         <v>646</v>
       </c>
       <c r="D312" s="4" t="s">
@@ -8260,7 +8268,7 @@
       <c r="B313" s="4" t="s">
         <v>650</v>
       </c>
-      <c r="C313" s="20" t="s">
+      <c r="C313" s="21" t="s">
         <v>646</v>
       </c>
       <c r="D313" s="4" t="s">
@@ -8512,7 +8520,7 @@
       <c r="B331" s="9" t="s">
         <v>686</v>
       </c>
-      <c r="C331" s="23">
+      <c r="C331" s="24">
         <v>86400</v>
       </c>
       <c r="D331" s="9" t="s">
@@ -8700,7 +8708,7 @@
       <c r="D344" s="3" t="s">
         <v>196</v>
       </c>
-      <c r="F344" s="24"/>
+      <c r="F344" s="25"/>
     </row>
     <row r="345" s="3" customFormat="1" ht="16.5" spans="1:6">
       <c r="A345" s="3">
@@ -8715,7 +8723,7 @@
       <c r="D345" s="3" t="s">
         <v>196</v>
       </c>
-      <c r="F345" s="24"/>
+      <c r="F345" s="25"/>
     </row>
     <row r="346" s="3" customFormat="1" ht="16.5" spans="1:6">
       <c r="A346" s="3">
@@ -8730,7 +8738,7 @@
       <c r="D346" s="3" t="s">
         <v>196</v>
       </c>
-      <c r="F346" s="24"/>
+      <c r="F346" s="25"/>
     </row>
     <row r="347" s="3" customFormat="1" spans="1:6">
       <c r="A347" s="3">
@@ -8809,7 +8817,7 @@
       <c r="B352" s="3" t="s">
         <v>734</v>
       </c>
-      <c r="C352" s="25" t="s">
+      <c r="C352" s="26" t="s">
         <v>735</v>
       </c>
       <c r="D352" s="3" t="s">
@@ -9209,7 +9217,7 @@
       <c r="B381" s="4" t="s">
         <v>791</v>
       </c>
-      <c r="C381" s="26" t="s">
+      <c r="C381" s="27" t="s">
         <v>792</v>
       </c>
       <c r="D381" s="4" t="s">
@@ -9354,7 +9362,7 @@
       <c r="A392" s="10">
         <v>870002</v>
       </c>
-      <c r="B392" s="27" t="s">
+      <c r="B392" s="28" t="s">
         <v>816</v>
       </c>
       <c r="C392" s="10">
